--- a/output/pdf_financials_xlsx/PERU.xlsx
+++ b/output/pdf_financials_xlsx/PERU.xlsx
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.152868</v>
+        <v>-0.152868</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.145103</v>
+        <v>-0.145103</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.074547</v>
+        <v>-0.074547</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.077033</v>
+        <v>-0.077033</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.047929</v>
+        <v>-0.047929</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-8.438001999999999</v>
@@ -1487,19 +1487,19 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.152868</v>
+        <v>-0.152868</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.145103</v>
+        <v>-0.145103</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.074547</v>
+        <v>-0.074547</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.077033</v>
+        <v>-0.077033</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.047929</v>
+        <v>-0.047929</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-8.438001999999999</v>
@@ -1649,19 +1649,19 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.152868</v>
+        <v>-0.152868</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.145103</v>
+        <v>-0.145103</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.074547</v>
+        <v>-0.074547</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.077033</v>
+        <v>-0.077033</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.047929</v>
+        <v>-0.047929</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-8.438001999999999</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>5.0956</v>
+        <v>-5.0956</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7.25515</v>
+        <v>-7.25515</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1877,19 +1877,19 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.152868</v>
+        <v>-0.152868</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.145103</v>
+        <v>-0.145103</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.074547</v>
+        <v>-0.074547</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.077033</v>
+        <v>-0.077033</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.047929</v>
+        <v>-0.047929</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-8.438001999999999</v>
@@ -1985,19 +1985,19 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.152868</v>
+        <v>-0.152868</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.145103</v>
+        <v>-0.145103</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.074547</v>
+        <v>-0.074547</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.077033</v>
+        <v>-0.077033</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.047929</v>
+        <v>-0.047929</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-8.416867999999999</v>
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -5469,28 +5469,28 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.104536</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.138641</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.138641</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.138641</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.138641</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.138641</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.143257</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.133947</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -5505,10 +5505,10 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.299156</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.687924</v>
       </c>
     </row>
     <row r="93">
@@ -9165,7 +9165,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11477,7 +11481,11 @@
           <t>Warrant reserve (Notes 8)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12567,7 +12575,11 @@
           <t>Warrant reserve (Notes 16)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -13350,7 +13362,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -36268,19 +36284,19 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>0.152868</v>
+        <v>-0.152868</v>
       </c>
       <c r="H319" s="5" t="n">
-        <v>0.145103</v>
+        <v>-0.145103</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>0.074547</v>
+        <v>-0.074547</v>
       </c>
       <c r="J319" s="5" t="n">
-        <v>0.077033</v>
+        <v>-0.077033</v>
       </c>
       <c r="K319" s="5" t="n">
-        <v>0.047929</v>
+        <v>-0.047929</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PERU.xlsx
+++ b/output/pdf_financials_xlsx/PERU.xlsx
@@ -1014,28 +1014,28 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.021671</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.086495</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.146062</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.02099</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.053818</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.032684</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.019027</v>
       </c>
     </row>
     <row r="13">
@@ -1892,28 +1892,28 @@
         <v>-0.047929</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-8.438001999999999</v>
+        <v>-8.459673</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-7.888413</v>
+        <v>-7.974908</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.613345</v>
+        <v>-5.759407</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.512696</v>
+        <v>-8.533685999999999</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-7.686141</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.482147</v>
+        <v>-3.535965</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.587519</v>
+        <v>-2.620203</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-10.004821</v>
+        <v>-10.023848</v>
       </c>
     </row>
     <row r="28">
@@ -2000,28 +2000,28 @@
         <v>-0.047929</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.416867999999999</v>
+        <v>-8.438539</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.799556</v>
+        <v>-7.886051</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.510823</v>
+        <v>-5.656885</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-8.410978999999999</v>
+        <v>-8.431969</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-7.558277</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.373434</v>
+        <v>-3.427252</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.490995</v>
+        <v>-2.523679</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-9.909176</v>
+        <v>-9.928203</v>
       </c>
     </row>
     <row r="30">
@@ -2261,25 +2261,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.178976</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.633314</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.499247</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.414633</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.343467</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.299332</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>13.159191</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>12.279037</v>
@@ -2294,13 +2294,13 @@
         <v>5.564165</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.251365</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.280298</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.158124</v>
       </c>
     </row>
     <row r="35">
@@ -2369,25 +2369,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.178976</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.633314</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.499247</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.414633</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.343467</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.299332</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>13.159191</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>12.279037</v>
@@ -2402,13 +2402,13 @@
         <v>5.564165</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.251365</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.280298</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.158124</v>
       </c>
     </row>
     <row r="37">
@@ -3017,22 +3017,22 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.206999</v>
+        <v>0.028023</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.647002</v>
+        <v>0.013688</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.507208</v>
+        <v>0.007960999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.418701</v>
+        <v>0.004068</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.347425</v>
+        <v>0.003958</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.301415</v>
+        <v>0.002083</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.374805</v>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -37779,7 +37779,11 @@
           <t>General and administrative (Note</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E336" s="5" t="n">
         <v>0.023541</v>
       </c>

--- a/output/pdf_financials_xlsx/PERU.xlsx
+++ b/output/pdf_financials_xlsx/PERU.xlsx
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.022596</v>
+        <v>0.091596</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.023187</v>
+        <v>0.026187</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.020309</v>
@@ -4086,13 +4086,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.294581</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.04946</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.120797</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -4260,16 +4260,16 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.042337</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.050056</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.057486</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.053233</v>
       </c>
       <c r="P70" s="3" t="n">
         <v>0</v>
@@ -4314,16 +4314,16 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.042337</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.050056</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.057486</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.053233</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -4530,16 +4530,16 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.042337</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.050056</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.057486</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.053233</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
@@ -4827,25 +4827,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.003615938587890445</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.004990439543710163</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.006622772910294296</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.005281043204693326</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -5914,16 +5906,16 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.005135</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.000527</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.00011</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0</v>
@@ -6184,16 +6176,16 @@
         <v>-0.07034799999999999</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.019361</v>
+        <v>0.024496</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.013498</v>
+        <v>-0.012971</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>9.3e-05</v>
+        <v>0.000203</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.005268</v>
+        <v>0.005349</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>0.029554</v>
@@ -6466,25 +6458,25 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.437395</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.5129050000000001</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09025900000000001</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.119463</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.178943</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00217</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001988</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -7756,25 +7748,25 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.437395</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.5129050000000001</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09025900000000001</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.119463</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.178943</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00217</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001988</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -7822,25 +7814,25 @@
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-6.734504</v>
+        <v>-7.171899</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-7.800347</v>
+        <v>-8.313252</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-5.114339</v>
+        <v>-5.204598</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-5.75575</v>
+        <v>-5.875213</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-6.90087</v>
+        <v>-7.079813</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-3.050824</v>
+        <v>-3.052994</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.981202</v>
+        <v>-1.98319</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-1.803741</v>
@@ -8744,7 +8736,11 @@
           <t>Current portion of lease obligation (Note 8)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -15037,7 +15033,11 @@
           <t>Leasehold improvements and purchase of equipment</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -15379,7 +15379,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -23238,7 +23242,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -26288,7 +26296,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -36887,7 +36899,11 @@
           <t>Consulting and director fees (Note 9)</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -37071,7 +37087,11 @@
           <t>Consulting and director fees (Note 8)</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
